--- a/tests/test_files/test_spreadsheet.xlsx
+++ b/tests/test_files/test_spreadsheet.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,20 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Тестовые данные</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Для проверки очистки метаданных</t>
+          <t>Secret Data</t>
         </is>
       </c>
     </row>
